--- a/05_statistics/frequency_audit_summary.xlsx
+++ b/05_statistics/frequency_audit_summary.xlsx
@@ -425,61 +425,81 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>run_timestamp_utc</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>model_name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>config_batch_size</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>config_temperature</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>source_priority</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>n_total_papers</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>n_final_include_yes</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>n_deepseek_sentence_reviewed_rows</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>n_fallback_not_sent_rows</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>n_failed_sentence_rows</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>n_deepseek_paper_summary_success</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>n_deepseek_paper_summary_failed</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>n_conflict_count</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>n_conflict_resolved</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>n_conflict_unresolved</t>
         </is>
@@ -488,37 +508,53 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>2026-05-24T19:05:22+00:00</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>deepseek-v4-flash</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>conflict_resolved_over_paper_level_ai_summary</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="F2" t="n">
         <v>24</v>
       </c>
-      <c r="C2" t="n">
+      <c r="G2" t="n">
         <v>13</v>
       </c>
-      <c r="D2" t="n">
+      <c r="H2" t="n">
         <v>184</v>
       </c>
-      <c r="E2" t="n">
+      <c r="I2" t="n">
         <v>419</v>
       </c>
-      <c r="F2" t="n">
+      <c r="J2" t="n">
         <v>0</v>
       </c>
-      <c r="G2" t="n">
+      <c r="K2" t="n">
         <v>24</v>
       </c>
-      <c r="H2" t="n">
+      <c r="L2" t="n">
         <v>0</v>
       </c>
-      <c r="I2" t="n">
+      <c r="M2" t="n">
         <v>6</v>
       </c>
-      <c r="J2" t="n">
+      <c r="N2" t="n">
         <v>6</v>
       </c>
-      <c r="K2" t="n">
+      <c r="O2" t="n">
         <v>0</v>
       </c>
     </row>

--- a/05_statistics/frequency_audit_summary.xlsx
+++ b/05_statistics/frequency_audit_summary.xlsx
@@ -508,7 +508,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-24T19:05:22+00:00</t>
+          <t>2026-05-24T19:39:19+00:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
